--- a/vignettes/vignette-1/donor_selection.xlsx
+++ b/vignettes/vignette-1/donor_selection.xlsx
@@ -522,32 +522,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1274_2015</t>
+          <t>2008_2018</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1274</v>
+        <v>2008</v>
       </c>
       <c r="D3" t="n">
-        <v>2015</v>
+        <v>2018</v>
       </c>
       <c r="E3" t="n">
-        <v>446.119</v>
+        <v>369.552</v>
       </c>
       <c r="F3" t="n">
-        <v>23.366</v>
+        <v>0.002</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05237615972419914</v>
+        <v>5.411958262977875e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4890486097902354</v>
+        <v>0.9613437180064304</v>
       </c>
       <c r="I3" t="n">
-        <v>0.972827</v>
+        <v>0.977604</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.114022</v>
+        <v>-0.302317</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
